--- a/output/第10期計画_内部確認結果への対応整理.xlsx
+++ b/output/第10期計画_内部確認結果への対応整理.xlsx
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査 問3</t>
+          <t>在宅生活改善調査（より適切と思われるサービス）</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>資料編に基準値のみ（20.4％・98票中20票）。24時間対応サービスの整備の判断材料として重要だが3年に1度でしか更新されない。年次評価には、区域内に事業所がないサービスの数（毎年度、北海道の指定事業所一覧で確認できる）を用いる。</t>
+          <t>資料編に基準値のみ（20.2％・99票中20票）。24時間対応サービスの整備の判断材料として重要だが3年に1度でしか更新されない。年次評価には、区域内に事業所がないサービスの数（毎年度、北海道の指定事業所一覧で確認できる）を用いる。</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査 問3</t>
+          <t>在宅生活改善調査（より適切と思われるサービス）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">

--- a/output/第10期計画_内部確認結果への対応整理.xlsx
+++ b/output/第10期計画_内部確認結果への対応整理.xlsx
@@ -3510,7 +3510,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ご指示の5つの観点で16項目を仕分けしたものです。本文の成果指標を12項目から8項目に絞り、毎年度、既存のデータで算定できる指標だけを本文に置く案です。残る8項目は、指標として廃止するもの、施策のアウトプットに置き換えるもの、計画期間の期末に1回確認するものに分けています。</t>
+          <t>ご指示の5つの観点で16項目を仕分けしたものです。本文の成果指標を12項目から7項目に絞り、毎年度、既存のデータで算定できる指標だけを本文に置く案です。残る10項目は、指標として廃止するもの、施策のアウトプットに置き換えるもの、計画期間の期末に1回確認するものに分けています。</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>他の指標と領域が重なるか、標本の偏り・把握率により基準値として用いにくいもの。3項目。数値は第2章の記述で用いる。</t>
+          <t>他の指標と領域が重なるか、標本の偏り・把握率により基準値として用いにくいもの。数値は第2章の記述で用いる。3項目。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>注1）本文の成果指標は12項目から6項目になり、補完指標4項目は廃止する。09シートの優先順位ではH04を本文に残すため7項目となる。資料1に基準値のみ掲げる指標が3項目である。注2）「取得頻度」が3年に1度の指標は、第10期の計画期間（令和9〜11年度）中に更新されない。次の調査は第11期計画の策定時（令和11年度）である。注3）保険料算定・介護保険運営に直接関係する事項（高齢者人口、要介護認定率、サービス見込量、給付費、保険料）は、代表KPIとは別に第2章・第6章で毎年度の実績と対比する。H01・H02・H03・H15がこれに対応する。注4）「KPI」という表現には、資料1の冒頭に「計画の達成状況を測るための指標」という用語説明を加え、第9期の代表KPI4項目との対応表を併せて示す。注5）本シートは受託者の案である。ご協議をお願いする。</t>
+          <t>注1）本文の成果指標は12項目から6項目になり、補完指標4項目は廃止する。09シートの優先順位ではH04を本文に残すため、本文の成果指標は7項目となる。資料1に基準値のみ掲げる指標が3項目である。注2）「取得頻度」が3年に1度の指標は、第10期の計画期間（令和9〜11年度）中に更新されない。次の調査は第11期計画の策定時（令和11年度）である。注3）保険料算定・介護保険運営に直接関係する事項（高齢者人口、要介護認定率、サービス見込量、給付費、保険料）は、代表KPIとは別に第2章・第6章で毎年度の実績と対比する。H01・H02・H03・H15がこれに対応する。注4）「KPI」という表現には、資料1の冒頭に「計画の達成状況を測るための指標」という用語説明を加え、第9期の代表KPI4項目との対応表を併せて示す。注5）本シートは受託者の案である。ご協議をお願いする。</t>
         </is>
       </c>
     </row>
